--- a/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
+++ b/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
@@ -450,7 +450,7 @@
         <v>86.17145539801147</v>
       </c>
       <c r="C2">
-        <v>83.91867379506178</v>
+        <v>81.84462228526009</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         <v>88.15374404331322</v>
       </c>
       <c r="C3">
-        <v>84.52236235319339</v>
+        <v>83.43212625615301</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>87.03357209905943</v>
       </c>
       <c r="C4">
-        <v>81.5208041931856</v>
+        <v>80.4537801752431</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         <v>82.5612987397275</v>
       </c>
       <c r="C5">
-        <v>76.89255652173912</v>
+        <v>75.72481404155398</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         <v>85.70506953925555</v>
       </c>
       <c r="C6">
-        <v>80.35807161106138</v>
+        <v>79.13760436737316</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v>89.24731182795699</v>
       </c>
       <c r="C7">
-        <v>85.45812663758861</v>
+        <v>84.19826577148011</v>
       </c>
     </row>
     <row r="8">
@@ -528,7 +528,7 @@
         <v>88.81601679390309</v>
       </c>
       <c r="C8">
-        <v>89.98039711071567</v>
+        <v>87.73071207097996</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
+++ b/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -365,10 +365,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>raw_region</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>tasa_neta</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>nacional</t>
         </is>
@@ -381,9 +386,12 @@
         </is>
       </c>
       <c r="B2">
+        <v>457567</v>
+      </c>
+      <c r="C2">
         <v>88.81588397200234</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>85.57956096322148</v>
       </c>
     </row>
@@ -394,9 +402,12 @@
         </is>
       </c>
       <c r="B3">
+        <v>442261</v>
+      </c>
+      <c r="C3">
         <v>84.72854969787767</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>80.67534083840127</v>
       </c>
     </row>
@@ -407,9 +418,12 @@
         </is>
       </c>
       <c r="B4">
+        <v>899828</v>
+      </c>
+      <c r="C4">
         <v>86.75884145165645</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>81.69211439336718</v>
       </c>
     </row>

--- a/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
+++ b/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
@@ -6,36 +6,77 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Global" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Regional" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Edades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Histórico" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Histórico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Histórico'!$A$1:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Histórico'!$A$1:$C$9</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
-  <si>
-    <t xml:space="preserve">Categoría</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t xml:space="preserve">Región</t>
   </si>
   <si>
     <t xml:space="preserve">Valor</t>
   </si>
   <si>
+    <t xml:space="preserve">Ranking</t>
+  </si>
+  <si>
     <t xml:space="preserve">Media nacional</t>
   </si>
   <si>
-    <t xml:space="preserve">Hombres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
+    <t xml:space="preserve">Ñuble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Araucanía</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Ríos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coquimbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biobío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O'Higgins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Lagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aysén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arica y Parinacota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atacama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarapacá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magallanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antofagasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metropolitana</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -44,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:22</t>
+    <t xml:space="preserve">2026-07-30 10:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -69,36 +110,6 @@
   </si>
   <si>
     <t xml:space="preserve">Año</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tramo de edad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor regional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor nacional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hasta 14 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 a 24 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 a 34 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35 a 44 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 a 54 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55 a 64 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desde 65 años</t>
   </si>
   <si>
     <t xml:space="preserve">Serie</t>
@@ -472,9 +483,10 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,42 +499,236 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>42.36</v>
+        <v>90.68</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>40.34</v>
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>81.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>44.41</v>
+        <v>89.67</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>42.79</v>
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>81.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>89.58</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>81.69</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>88.64</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>81.69</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="D6" s="2" t="n">
+        <v>81.69</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>87.01</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>81.69</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="n">
         <v>86.76</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>81.69</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>86.65</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>81.69</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>86.57</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>81.69</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>86.47</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>81.69</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>86.05</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>81.69</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>84.07</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>81.69</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>81.69</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>81.69</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>76.55</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>81.69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>74.57</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" s="2" t="n">
         <v>81.69</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C4"/>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -539,7 +745,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -547,50 +753,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -604,111 +810,6 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>86.17</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>81.84</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>88.15</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>83.43</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>87.03</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>80.45</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>82.56</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>75.72</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>85.71</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>79.14</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>89.25</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>84.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>88.82</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>87.73</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C8"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
@@ -716,10 +817,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -730,7 +831,7 @@
         <v>2021</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>84.09</v>
@@ -741,7 +842,7 @@
         <v>2021</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>78.5</v>
@@ -752,7 +853,7 @@
         <v>2022</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>84.62</v>
@@ -763,7 +864,7 @@
         <v>2022</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>78.97</v>
@@ -774,7 +875,7 @@
         <v>2023</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>86.76</v>
@@ -785,7 +886,7 @@
         <v>2023</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>81.69</v>
@@ -796,7 +897,7 @@
         <v>2024</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>87.02</v>
@@ -807,7 +908,7 @@
         <v>2024</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>82</v>

--- a/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
+++ b/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 10:50</t>
+    <t xml:space="preserve">2026-07-31 11:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
+++ b/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-31 11:41</t>
+    <t xml:space="preserve">2026-08-19 13:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -113,9 +113,6 @@
   </si>
   <si>
     <t xml:space="preserve">Serie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Region</t>
   </si>
   <si>
     <t xml:space="preserve">Nacional</t>
@@ -831,7 +828,7 @@
         <v>2021</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>84.09</v>
@@ -842,7 +839,7 @@
         <v>2021</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>78.5</v>
@@ -853,7 +850,7 @@
         <v>2022</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>84.62</v>
@@ -864,7 +861,7 @@
         <v>2022</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>78.97</v>
@@ -875,7 +872,7 @@
         <v>2023</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>86.76</v>
@@ -886,7 +883,7 @@
         <v>2023</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>81.69</v>
@@ -897,7 +894,7 @@
         <v>2024</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>87.02</v>
@@ -908,7 +905,7 @@
         <v>2024</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>82</v>

--- a/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
+++ b/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:55</t>
+    <t xml:space="preserve">2026-08-28 15:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
+++ b/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:02</t>
+    <t xml:space="preserve">2026-08-29 05:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
+++ b/output/graficos_regionales_salud/plot_s_fonasa_a_2023_o_higgins.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:39</t>
+    <t xml:space="preserve">2026-09-06 18:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
